--- a/outputs/Block5_House_Distribution.xlsx
+++ b/outputs/Block5_House_Distribution.xlsx
@@ -453,13 +453,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>-0.03694832434740891</v>
+        <v>0.01491156870087162</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -467,13 +467,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>1.699906626866217</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0.2820732968571464</v>
+        <v>0.4987195719777766</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -481,13 +481,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-0.1648931557853732</v>
+        <v>0.04232832252854557</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -495,13 +495,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>5.586198698614951</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>0.3545840920074594</v>
+        <v>-0.269620245019544</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -509,13 +509,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="C6">
         <v>19</v>
       </c>
       <c r="D6">
-        <v>-0.2130202719963314</v>
+        <v>-0.2006467456771617</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -523,13 +523,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>1.550377686812013</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0.433187337447319</v>
+        <v>0.1400942697955107</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -537,13 +537,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>172.6467820636017</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="C8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D8">
-        <v>-0.4769462223457026</v>
+        <v>0.01929604709013688</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -551,13 +551,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>-0.1780367518371049</v>
+        <v>-0.2450827893961431</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -565,13 +565,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>3.475459163737268</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>-0.4401936139338187</v>
+        <v>0.409407880120741</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -579,13 +579,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>-0.5287224693580312</v>
+        <v>0.4427846049148738</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -593,13 +593,13 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="C12">
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0.1478640668473066</v>
+        <v>-0.1147345811896248</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -607,13 +607,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13">
-        <v>0.229836946441103</v>
+        <v>-0.2240926546957844</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -621,13 +621,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="C14">
         <v>15</v>
       </c>
       <c r="D14">
-        <v>0.1470436791808698</v>
+        <v>0.2188743955707473</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -635,13 +635,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>4.801946011202828</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15">
-        <v>0.2467794257059026</v>
+        <v>-0.11811531334273</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -649,13 +649,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="C16">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D16">
-        <v>0.1918505851803616</v>
+        <v>-0.4018190334304563</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -663,13 +663,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17">
-        <v>0.005541379936312207</v>
+        <v>-0.2123052979477622</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5_House_Distribution.xlsx
+++ b/outputs/Block5_House_Distribution.xlsx
@@ -453,13 +453,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.966548112280941</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.01491156870087162</v>
+        <v>-0.4028978914405681</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -467,13 +467,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>1.473024875335867</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0.4987195719777766</v>
+        <v>-0.3755970214977782</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -481,13 +481,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>9.770258645592461</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>0.04232832252854557</v>
+        <v>-0.02763797146606439</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -495,13 +495,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>5.170440884727479</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>-0.269620245019544</v>
+        <v>0.33141261676163</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -509,13 +509,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>18.83927196478475</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="C6">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>-0.2006467456771617</v>
+        <v>0.2282296274527074</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -523,13 +523,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.8437214709471421</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>0.1400942697955107</v>
+        <v>0.2139607295338708</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -537,13 +537,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>173.6497555759981</v>
+        <v>181.348317089571</v>
       </c>
       <c r="C8">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D8">
-        <v>0.01929604709013688</v>
+        <v>-0.1997118794436403</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -551,13 +551,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0.2404700937671027</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>-0.2450827893961431</v>
+        <v>0.2322417900998337</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -565,13 +565,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>3.656634670288002</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10">
-        <v>0.409407880120741</v>
+        <v>0.24980091788641</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -579,13 +579,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>2.604250820161925</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>0.4427846049148738</v>
+        <v>-0.009428890891545194</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -593,13 +593,13 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>13.3559567781861</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>-0.1147345811896248</v>
+        <v>0.04754139896378362</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -607,13 +607,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>4.301787319744047</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>-0.2240926546957844</v>
+        <v>0.06768685283428155</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -621,13 +621,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>15.0529980979447</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>0.2188743955707473</v>
+        <v>0.1943471375318673</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -635,13 +635,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>5.212253933741241</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>-0.11811531334273</v>
+        <v>-0.4571942561654811</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -649,13 +649,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>175.5728436009487</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="C16">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16">
-        <v>-0.4018190334304563</v>
+        <v>0.4278210255567672</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -663,13 +663,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>4.289783155551396</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17">
-        <v>-0.2123052979477622</v>
+        <v>-0.520574185716101</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5_House_Distribution.xlsx
+++ b/outputs/Block5_House_Distribution.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+          <t>69084551907b520052181adf33e09563f086f0b6de4f1d95d2e192b06c14159d</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T02:41:23.457320+00:00</t>
+          <t>2026-10-24T07:22:07.989106+00:00</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20T06:09:32.147340+00:00</t>
+          <t>2026-10-24T07:24:45.840036+00:00</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20T06:11:56.240312+00:00</t>
+          <t>2026-10-24T07:26:59.123079+00:00</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+          <t>35-race structural motor + polling enrichment on 15 monitored races</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+          <t>Public Senate map highlights 15 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recovered Model(5).xlsx / Senate Historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration rows</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration reference SHA256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7b3f807a5128485c7fd4de43f99733784af9627e835db4777c047b68e762feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senate production policy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recovered 5B calibration + 15 current monitored races; automatic structural blending disabled</t>
         </is>
       </c>
     </row>
@@ -896,7 +942,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -920,7 +966,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+          <t>8a7bfde9efafe267b78417530287877a5e160939951e8ae39d62138f60d4e05a</t>
         </is>
       </c>
     </row>
@@ -932,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T06:12:00.987520+00:00</t>
+          <t>2026-10-24T07:27:04.098692+00:00</t>
         </is>
       </c>
     </row>
